--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_04_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_14_AI Evaluation _ Benchmarking/Day_14_Phan_04_18_Cau.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -939,7 +939,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ cộng hai ô hai version cho kết quả khác nhau.</t>
+          <t>Trong bảng 2x2 cho McNemar / exact-binomial test, số discordant pairs (cặp bất đồng) là tổng của hai ô chéo ngoài: b + c = 10 + 22 = 32.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1285,7 +1285,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng cost component trước khi cộng.</t>
+          <t>Tổng direct evaluation cost: (500 checks * $0) + (200 judge calls * $0,02) + (20 human reviews * $2) = $0 + $4 + $40 = 44 USD.</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -1340,7 +1340,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một aggregate win có thể che regression nào?</t>
+          <t>Điều kiện cần thiết của một release gate có thể tái lập: (a) Khóa phiên bản baseline và bộ test suite, (b) so sánh chênh lệch metric trên cùng tập ca kiểm thử (paired delta), (c) đặt ngưỡng bắt buộc cho các phân khúc trọng yếu (critical slice) và an toàn, (d) có quy tắc rõ ràng xử lý độ không chắc chắn.</t>
         </is>
       </c>
     </row>
